--- a/Task_08/DucNVFX14814_CN4_Review_Checklist.xlsx
+++ b/Task_08/DucNVFX14814_CN4_Review_Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Funix\4. CC4\5. LAB301x\LAB301x_01\Task_08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF7E60C7-AEC5-43B7-B220-D6EEF5C6A13A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B10E92D-FBBB-4961-B070-A1D604E379DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="32">
   <si>
     <t>CHECKLIST TỰ KIỂM TRA - TASK 8: CN4 ĐỀ XUẤT SỐ VÉ SỐ NÊN MUA</t>
   </si>
@@ -111,10 +111,25 @@
     <t>Chưa thực hiện:</t>
   </si>
   <si>
-    <t>Đã tạo các unit test và chạy cho các lớp DAO</t>
-  </si>
-  <si>
     <t>Đã tạo các unit test và chạy cho các lớp DAO, đầy đủ các method được dùng trong hệ thống</t>
+  </si>
+  <si>
+    <t>Đã tạo các unit test và chạy cho các lớp DAO và BO</t>
+  </si>
+  <si>
+    <t>Đã tạo chức tra chạy cho các lớp DAO và BO</t>
+  </si>
+  <si>
+    <t>Đã tạo tình kiểm chạy cho các lớp DAO và BO</t>
+  </si>
+  <si>
+    <t>Đã tạo chạy cho các lớp DAO và BO</t>
+  </si>
+  <si>
+    <t>Đã tạo quán sửa chạy cho các lớp DAO và BO</t>
+  </si>
+  <si>
+    <t>Đã tạo các unit test và chạy cho các lớp DAO và BO, đầy đủ các method được dùng trong hệ thống</t>
   </si>
 </sst>
 </file>
@@ -235,12 +250,6 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -258,6 +267,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -529,244 +544,244 @@
   <dimension ref="A1:F19"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.5546875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="4.21875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="54" style="3" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="45" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="8.6640625" style="3"/>
+    <col min="1" max="1" width="3.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="54" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="45" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:6" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+    </row>
+    <row r="2" spans="1:6" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
     </row>
     <row r="4" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="E4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="6">
+      <c r="B5" s="4">
         <v>1</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="8"/>
+      <c r="E5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="6">
+      <c r="B6" s="4">
         <v>2</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="8"/>
+      <c r="E6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="6"/>
     </row>
     <row r="7" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="6">
+      <c r="B7" s="4">
         <v>3</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="8"/>
+      <c r="E7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="6"/>
     </row>
     <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="6">
+      <c r="B8" s="4">
         <v>4</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="8"/>
+      <c r="E8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="6"/>
     </row>
     <row r="9" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="6">
-        <v>5</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="B9" s="4">
+        <v>5</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="8"/>
+      <c r="E9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="6"/>
     </row>
     <row r="10" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="6">
+      <c r="B10" s="4">
         <v>6</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>25</v>
+      <c r="E10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="6">
+      <c r="B11" s="4">
         <v>7</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>26</v>
+      <c r="E11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="6">
+      <c r="B12" s="4">
         <v>8</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" s="8"/>
+      <c r="E12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="6">
+      <c r="B13" s="4">
         <v>9</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" s="8"/>
+      <c r="E13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="6"/>
     </row>
     <row r="14" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="6">
+      <c r="B14" s="4">
         <v>10</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="8"/>
+      <c r="E14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="6">
+      <c r="B15" s="4">
         <v>11</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="8"/>
+      <c r="E15" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="6"/>
     </row>
     <row r="17" spans="3:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="8">
         <f>COUNTA(E5:E15)</f>
         <v>11</v>
       </c>
     </row>
     <row r="18" spans="3:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="8">
         <f>COUNTIF(E5:E15,"Đã thực hiện")</f>
         <v>11</v>
       </c>
     </row>
     <row r="19" spans="3:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="8">
         <f>COUNTIF(E5:E15,"Chưa thực hiện")</f>
         <v>0</v>
       </c>
